--- a/recipes/Chamber-K 공정레시피 샘플.xlsx
+++ b/recipes/Chamber-K 공정레시피 샘플.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,26 +27,43 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="13"/>
+      <color rgb="00C55A11"/>
+      <sz val="11"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="5">
@@ -58,7 +75,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
@@ -68,7 +85,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -98,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -107,14 +124,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -189,36 +212,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Chamber-K</author>
-  </authors>
-  <commentList>
-    <comment ref="S1" authorId="0" shapeId="0">
-      <text>
-        <t>T 이면 이 공정에서 히터를 사용합니다.
-비우거나 F 이면 히터 미사용 (기존 레시피와 동일 동작).</t>
-      </text>
-    </comment>
-    <comment ref="T1" authorId="0" shapeId="0">
-      <text>
-        <t>목표 온도 [°C]. 0 ~ HEATER_MAX_TEMP(기본 500).
-가스 유량이 안정된 뒤 이 온도까지 승온하고,
-도달을 확인한 다음에야 파워를 켭니다.</t>
-      </text>
-    </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
-      <text>
-        <t>승온 속도 [°C/min]. 비우면 config 기본값(12).
-PLC 분해능이 6°C/min 이라 6의 배수로 쓰는 것이 정확합니다.
-실측: 상한 600에서 상온→300°C 약 45분, 150→300°C 약 27분.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -513,30 +506,30 @@
   <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -647,7 +640,7 @@
       <c r="A2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>delay 0.0001m</t>
         </is>
@@ -666,29 +659,29 @@
       <c r="N2" s="3" t="n"/>
       <c r="O2" s="3" t="n"/>
       <c r="P2" s="3" t="n"/>
-      <c r="Q2" s="3" t="n"/>
-      <c r="R2" s="3" t="n"/>
-      <c r="S2" s="4" t="n"/>
-      <c r="T2" s="4" t="n"/>
-      <c r="U2" s="4" t="n"/>
+      <c r="Q2" s="4" t="n"/>
+      <c r="R2" s="4" t="n"/>
+      <c r="S2" s="5" t="n"/>
+      <c r="T2" s="5" t="n"/>
+      <c r="U2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Au</t>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>SiO2_RF_300C</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.5</v>
+        <v>20</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -697,31 +690,29 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>T</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
       <c r="N3" s="3" t="n">
@@ -729,33 +720,33 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
           <t>F</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>SiO2</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>Ti</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>Au</t>
-        </is>
-      </c>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="T3" s="4" t="n">
+      <c r="T3" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="U3" s="5" t="n">
         <v>12</v>
       </c>
     </row>
@@ -763,16 +754,16 @@
       <c r="A4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Au_400C</t>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Au_DC_400C</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>1</v>
@@ -790,9 +781,7 @@
       <c r="H4" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="I4" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -803,46 +792,44 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
           <t>F</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>Ti</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>SiO2</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>Au</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="S4" s="5" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="T4" s="4" t="n">
+      <c r="T4" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="U4" s="4" t="n">
+      <c r="U4" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -850,7 +837,7 @@
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Au_no_heat</t>
         </is>
@@ -859,7 +846,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>1</v>
@@ -877,9 +864,7 @@
       <c r="H5" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="I5" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -898,9 +883,7 @@
           <t>F</t>
         </is>
       </c>
-      <c r="N5" s="3" t="n">
-        <v>200</v>
-      </c>
+      <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
           <t>F</t>
@@ -911,40 +894,26 @@
           <t>T</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>Ti</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>SiO2</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>Au</t>
         </is>
       </c>
-      <c r="S5" s="4" t="inlineStr">
+      <c r="S5" s="5" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="T5" s="4" t="n"/>
-      <c r="U5" s="4" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="F2:F200 G2:G200 J2:J200 L2:L200 M2:M200 O2:O200 P2:P200 S2:S200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="T / F" prompt="T = 사용, F = 미사용 (비워두면 F)" type="list">
-      <formula1>"T,F"</formula1>
-    </dataValidation>
-    <dataValidation sqref="T2:T200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="목표 온도 범위 초과" error="heater_temp 는 0 ~ 500°C 범위여야 합니다 (config_user.json 의 HEATER_MAX_TEMP)." type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>500</formula2>
-    </dataValidation>
-    <dataValidation sqref="U2:U200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="램프 속도 범위" error="heater_ramp 는 6 ~ 60 °C/min. 비우면 config 기본값(12)을 씁니다.&#10;6의 배수 권장 (PLC 분해능이 6°C/min)." type="decimal" operator="between">
-      <formula1>6</formula1>
-      <formula2>60</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -954,230 +923,512 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A35"/>
+  <dimension ref="A1:A77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="108" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Chamber-K 공정 레시피 — 작성 방법</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr"/>
+      <c r="A2" s="7" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>■ 기본 규칙</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>· Recipe 시트의 1행(헤더)은 절대 바꾸지 마세요. 프로그램이 이 이름으로 컬럼을 찾습니다.</t>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · Recipe 시트의 1행(헤더)은 절대 바꾸지 마세요. 프로그램이 이 이름으로 컬럼을 찾습니다.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>· 2행부터 한 줄이 공정 하나입니다. 위에서 아래로 순서대로 실행됩니다.</t>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 2행부터 한 줄이 공정 하나입니다. 위에서 아래로 순서대로 실행됩니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>· T = 사용, F = 미사용. 비워두면 F 로 봅니다.</t>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · T = 사용, F = 미사용. 비워두면 F 로 봅니다. (1/0, Y/N, TRUE/FALSE, ON 도 인식)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>· Process_name 에 'delay 30m' 형태로 쓰면 그 줄은 대기 스텝이 됩니다 (s/m/h/d 사용 가능).</t>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · Process_name 에 'delay 30m' 형태로 쓰면 그 줄은 대기 스텝이 됩니다 (s / m / h / d).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>· 노란색 칸이 히터 관련 항목입니다. 기존 레시피에 이 3개 컬럼만 추가된 것이고,</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · '#' 컬럼은 표시용 번호일 뿐 프로그램은 읽지 않습니다. 이 칸만 채운 줄은 건너뜁니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  컬럼이 아예 없거나 비어 있으면 히터를 쓰지 않던 예전과 똑같이 동작합니다.</t>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 주황색 칸이 히터 관련 3개 컬럼입니다. 컬럼이 아예 없거나 비어 있으면</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr"/>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     히터를 쓰지 않던 예전 레시피와 똑같이 동작합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>■ 히터 컬럼 3개</t>
-        </is>
-      </c>
+      <c r="A11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>use_heater   T 이면 이 공정에서 히터 사용</t>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>■ 컬럼</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>heater_temp  목표 온도 [°C], 0 ~ 500</t>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Process_name       공정 이름. 로그·구글챗·ChK_log.csv 에 그대로 남습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>heater_ramp  승온 속도 [°C/min], 비우면 12. 6의 배수 권장</t>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   working_pressure   작업 압력 [mTorr]. 필수, 0 보다 커야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr"/>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   process_time       증착 시간 [분].</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>■ 히터를 쓰면 공정이 이렇게 진행됩니다</t>
+          <t xml:space="preserve">   shutter_delay      셔터 대기 시간 [분]. 비우면 0.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>1. 배기 → 가스 밸브 열기 → 유량 설정 → 유량 ON</t>
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ★ process_time 과 shutter_delay 중 하나는 반드시 0 보다 커야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>2. 여기서 히터 목표·램프 속도를 PLC 에 보내고 승온을 시작합니다 (압력 안정화와 동시 진행)</t>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Ar / O2            가스 사용 여부. 둘 중 하나 이상 T 여야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>3. 목표 ±3°C 안에 60초 연속 머물면 '도달' 로 판정</t>
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Ar_flow / O2_flow  유량 [sccm]. 해당 가스가 T 면 0 보다 커야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>4. 도달한 뒤에야 건 셔터 / 파워 / 압력 step-down 으로 넘어갑니다</t>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   use_dc_power       DC 파워 사용 여부</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>5. 공정이 끝나거나 STOP 을 누르면 히터가 자동으로 꺼집니다</t>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   dc_power           DC 파워 [W]. use_dc_power=T 면 0 보다 커야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr"/>
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   use_dc_delay       DC 안정화 대기 사용 여부 (use_dc_power=T 일 때만 의미 있음)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>※ 히터는 진공 인터락이 걸려 있어 진공이 잡히기 전에는 켜지지 않습니다.</t>
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   use_rf_power       RF 파워 사용 여부</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   그래서 '배기 전 예열' 은 불가능하고, 위 2번이 가능한 가장 빠른 시점입니다.</t>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   rf_power           RF 파워 [W]. use_rf_power=T 면 0 보다 커야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr"/>
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                      ※ RF Offset / Param 은 레시피가 아니라 프로그램 화면의 값을 씁니다.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>■ 승온에 걸리는 시간 (2026-09-01 실측, DAC 상한 600)</t>
+          <t xml:space="preserve">   gun1 / gun2        건 셔터 사용 여부</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>상온(25°C) → 150°C   약 11분</t>
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   G1 Target / G2 Target   타겟 이름(문자열). 제어에는 쓰이지 않고 로그·ERP 보고에만 남습니다.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>150°C → 300°C        약 27분   (전류 22.4A, 도달 후 20.0A 로 하강)</t>
-        </is>
-      </c>
+      <c r="A28" s="7" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>상온 → 300°C          약 45분</t>
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>■ 히터 컬럼 3개</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>→ 승온 시간이 긴 공정은 process_time 과 별개로 전체 소요가 늘어납니다.</t>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   use_heater    T 이면 이 공정에서 히터를 사용합니다.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr"/>
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   heater_temp   목표 온도 [°C]. 0 초과 ~ 700 (config_user.json 의 HEATER_MAX_TEMP).</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">   heater_ramp   승온 속도 [°C/min]. 비우면 기본값 12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 6 미만은 6 으로 자동 보정, 60 초과는 오류입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 PLC 램프는 1카운트/초 = 6°C/min 단위라 6의 배수로 반올림됩니다 (10 → 12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ★ 히터 레시피(히터 전용 파일)에 있는 '느린 램프(6 미만)' 는 공정 레시피에는 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>■ 히터를 쓰면 공정이 이 순서로 진행됩니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   1. 이전 공정 잔류 방지 — DC / RF Power OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2. 각 채널 Flow OFF → MFC 메인 밸브 Open  (배기를 최대로 열어 둡니다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   3. 히터 램프 속도 · 목표 온도를 PLC 에 보내고 승온 시작</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      ★ 가스를 넣기 전, 고진공 상태에서 올립니다. 아웃가싱이 배기로 빠진 뒤에</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        공정 가스를 도입하기 위해서입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   4. 도달 대기 — 램프가 최종 목표에 닿고, 현재 온도가 목표 ±1.0°C 안에</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      60초 연속 머물면 '도달' 로 봅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   5. 도달한 뒤에 MFC / Power Supply 영점 → 가스 밸브 Open → 유량 설정 · Flow ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   6. 압력 제어(SP1) → 건 셔터 → 파워 → shutter_delay → process_time</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   7. 공정이 끝나거나 STOP 을 누르면 히터가 자동으로 꺼지고, 램프 속도도 기본값으로 돌아갑니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ★ 스텝이 끝날 때마다 히터가 꺼집니다. 다음 스텝이 같은 온도를 써도 처음부터 다시 승온합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     연속 스텝에서 온도를 계속 유지하려면, 공정 레시피의 히터 칸은 비워 두고</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     히터 전용 레시피를 따로 돌리세요 (두 레시피는 동시에 돌아갑니다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ※ 히터는 진공 인터락이 걸려 있어 진공이 잡히기 전에는 켜지지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      그래서 '배기 전 예열' 은 불가능하고, 위 3번이 가능한 가장 빠른 시점입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>■ 도달 대기 타임아웃</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   기본 5400초(90분). 예상 승온 시간 + 30분 이 그보다 크면 그쪽을 씁니다 (최대 12시간).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   넘기면 '히터 승온 timeout' 으로 그 공정을 중단합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>■ 승온에 걸리는 시간 (상온 25°C 출발, 설정값 기준 계산)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        목표        12°C/min      6°C/min</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        150°C        11.3분        20.8분</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        300°C        23.8분        45.8분</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        400°C        32.1분        62.5분</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        600°C        48.8분        95.8분</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        700°C        57.1분       112.5분</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   목표 직전 10°C 는 오버슈트를 줄이려고 6°C/min 으로 낮춰 접근합니다. 위 값에 포함돼 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   → 승온 시간은 process_time 과 별개로 전체 소요에 그대로 더해집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ※ 2026-09-01 실측(상온→300°C 약 45분)은 DAC 상한이 600 이던 시절 파워가 모자라</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     램프가 뒤처졌던 값입니다. 상한을 1200 으로 올린 뒤로는 설정 램프를 따라갑니다(2026-09-02 600°C 확인).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
           <t>■ 저장할 때</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>· 이 파일 그대로 .xlsx 로 저장해서 프로그램의 [Select File] 로 열면 됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>· .csv 로 저장해도 동작합니다 (헤더 이름만 같으면 됨).</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>· 시트가 여러 개면 'Recipe' 시트를 먼저 찾고, 없으면 첫 번째 시트를 씁니다.</t>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 이 파일 그대로 .xlsx 로 저장해서 프로그램의 [Select File] 로 열면 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · .csv 로 저장해도 동작합니다 (헤더 이름만 같으면 됩니다, UTF-8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 시트가 여러 개면 'Recipe' 시트를 먼저 찾고, 없으면 첫 번째 시트를 씁니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 레시피 시트에는 헤더와 데이터 행만 두세요. 합계·메모 행은 넣지 마세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>작성 2026-09-04 · 관련 설정: config_user.json 의 HEATER_* 항목</t>
         </is>
       </c>
     </row>

--- a/recipes/Chamber-K 공정레시피 샘플.xlsx
+++ b/recipes/Chamber-K 공정레시피 샘플.xlsx
@@ -923,7 +923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A77"/>
+  <dimension ref="A1:A78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="108" customWidth="1" min="1" max="1"/>
@@ -1264,169 +1264,176 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="n"/>
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     단, 히터 레시피가 가스·압력을 쓰는 중이면 공정을 시작할 수 없습니다 (MFC 공유).</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ※ 히터는 진공 인터락이 걸려 있어 진공이 잡히기 전에는 켜지지 않습니다.</t>
-        </is>
-      </c>
+      <c r="A52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">   ※ 히터는 진공 인터락이 걸려 있어 진공이 잡히기 전에는 켜지지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">      그래서 '배기 전 예열' 은 불가능하고, 위 3번이 가능한 가장 빠른 시점입니다.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="7" t="n"/>
-    </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="7" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>■ 도달 대기 타임아웃</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   기본 5400초(90분). 예상 승온 시간 + 30분 이 그보다 크면 그쪽을 씁니다 (최대 12시간).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">   기본 5400초(90분). 예상 승온 시간 + 30분 이 그보다 크면 그쪽을 씁니다 (최대 12시간).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">   넘기면 '히터 승온 timeout' 으로 그 공정을 중단합니다.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="7" t="n"/>
-    </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="7" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>■ 승온에 걸리는 시간 (상온 25°C 출발, 설정값 기준 계산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        목표        12°C/min      6°C/min</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        150°C        11.3분        20.8분</t>
+          <t xml:space="preserve">        목표        12°C/min      6°C/min</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        300°C        23.8분        45.8분</t>
+          <t xml:space="preserve">        150°C        11.3분        20.8분</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        400°C        32.1분        62.5분</t>
+          <t xml:space="preserve">        300°C        23.8분        45.8분</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        600°C        48.8분        95.8분</t>
+          <t xml:space="preserve">        400°C        32.1분        62.5분</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        700°C        57.1분       112.5분</t>
+          <t xml:space="preserve">        600°C        48.8분        95.8분</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   목표 직전 10°C 는 오버슈트를 줄이려고 6°C/min 으로 낮춰 접근합니다. 위 값에 포함돼 있습니다.</t>
+          <t xml:space="preserve">        700°C        57.1분       112.5분</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">   목표 직전 10°C 는 오버슈트를 줄이려고 6°C/min 으로 낮춰 접근합니다. 위 값에 포함돼 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">   → 승온 시간은 process_time 과 별개로 전체 소요에 그대로 더해집니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ※ 2026-09-01 실측(상온→300°C 약 45분)은 DAC 상한이 600 이던 시절 파워가 모자라</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">   ※ 2026-09-01 실측(상온→300°C 약 45분)은 DAC 상한이 600 이던 시절 파워가 모자라</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">     램프가 뒤처졌던 값입니다. 상한을 1200 으로 올린 뒤로는 설정 램프를 따라갑니다(2026-09-02 600°C 확인).</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="7" t="n"/>
-    </row>
     <row r="71">
-      <c r="A71" s="8" t="inlineStr">
+      <c r="A71" s="7" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>■ 저장할 때</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 이 파일 그대로 .xlsx 로 저장해서 프로그램의 [Select File] 로 열면 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · .csv 로 저장해도 동작합니다 (헤더 이름만 같으면 됩니다, UTF-8).</t>
+          <t xml:space="preserve">   · 이 파일 그대로 .xlsx 로 저장해서 프로그램의 [Select File] 로 열면 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · 시트가 여러 개면 'Recipe' 시트를 먼저 찾고, 없으면 첫 번째 시트를 씁니다.</t>
+          <t xml:space="preserve">   · .csv 로 저장해도 동작합니다 (헤더 이름만 같으면 됩니다, UTF-8).</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">   · 시트가 여러 개면 'Recipe' 시트를 먼저 찾고, 없으면 첫 번째 시트를 씁니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">   · 레시피 시트에는 헤더와 데이터 행만 두세요. 합계·메모 행은 넣지 마세요.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="7" t="n"/>
-    </row>
     <row r="77">
-      <c r="A77" s="11" t="inlineStr">
+      <c r="A77" s="7" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="inlineStr">
         <is>
           <t>작성 2026-09-04 · 관련 설정: config_user.json 의 HEATER_* 항목</t>
         </is>
